--- a/lab5/I14241.xlsx
+++ b/lab5/I14241.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/magdalenasmietana/Documents/Fizyka/Fizyka-Lab/lab5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96F9FBBD-93DE-6348-A88D-BA3523056C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{404D9B38-AA1E-9A49-AEFB-C61F8EB4D5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{74161D42-4EDB-574E-967C-38FE284EC8F3}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{EAD3DAE9-F3B0-42A3-9A8C-F6FE9E4DE356}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,24 +35,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>Lp.</t>
+  </si>
   <si>
     <t>Liczba zwojów N</t>
   </si>
   <si>
-    <t>Natężenie I [A]</t>
-  </si>
-  <si>
-    <t>Kąt wychylenia w lewo</t>
-  </si>
-  <si>
-    <t>Kąt wychylenia w prawo</t>
-  </si>
-  <si>
-    <t>Średnia kątów wychylenia</t>
-  </si>
-  <si>
-    <t>Indukcja magnetyczna B [μT]</t>
+    <t>Prąd I [mA]</t>
+  </si>
+  <si>
+    <t>Kąt wychylenia w lewo alfa [st]</t>
+  </si>
+  <si>
+    <t>Kąt wychylenia w prawo alfa [st]</t>
+  </si>
+  <si>
+    <t>Średni kąt wychylenia</t>
+  </si>
+  <si>
+    <t>B_0 [muT]</t>
+  </si>
+  <si>
+    <t>mu_0</t>
+  </si>
+  <si>
+    <t>srednica cewki [mm]</t>
+  </si>
+  <si>
+    <t>B_0</t>
+  </si>
+  <si>
+    <t>[metry]</t>
+  </si>
+  <si>
+    <t>b_0 srednie</t>
+  </si>
+  <si>
+    <t>(B_i - B_0_sr)^2</t>
+  </si>
+  <si>
+    <t>niepewnosc pomiarowa u_A</t>
   </si>
 </sst>
 </file>
@@ -61,10 +85,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -88,17 +113,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -117,9 +133,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Pakiet Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -127,39 +143,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Pakiet Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -211,7 +227,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -263,7 +279,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Pakiet Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -322,13 +338,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -337,6 +346,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -401,136 +417,596 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9217BD20-AC8B-4945-99FF-81C5F5B5C74B}">
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18C9B7A9-41F0-4316-96C5-F937DA481D86}">
+  <dimension ref="F6:M40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.5" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.1640625" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" customWidth="1"/>
-    <col min="5" max="5" width="26.6640625" customWidth="1"/>
-    <col min="6" max="6" width="30.33203125" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" customWidth="1"/>
+    <col min="8" max="8" width="11.5" customWidth="1"/>
+    <col min="9" max="9" width="28.33203125" customWidth="1"/>
+    <col min="10" max="10" width="28.83203125" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="10.1640625" customWidth="1"/>
+    <col min="13" max="13" width="16.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="6" spans="6:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="G6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
+      <c r="L6" t="s">
+        <v>6</v>
+      </c>
+      <c r="M6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="6:13" x14ac:dyDescent="0.2">
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>40</v>
+      </c>
+      <c r="H7">
+        <v>56</v>
+      </c>
+      <c r="I7">
+        <v>28</v>
+      </c>
+      <c r="J7">
+        <v>25</v>
+      </c>
+      <c r="K7">
+        <f t="shared" ref="K7:K30" si="0">(I7+J7)/2</f>
+        <v>26.5</v>
+      </c>
+      <c r="L7">
+        <f>($K$36*G7*H7)/($K$35*TAN(RADIANS(K7)))*POWER(10,6)</f>
+        <v>21.714422335965708</v>
+      </c>
+      <c r="M7">
+        <f>POWER(L7 - $K$33,2)</f>
+        <v>9.6006117701817564E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="6:13" x14ac:dyDescent="0.2">
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>40</v>
+      </c>
+      <c r="H8">
+        <v>90</v>
+      </c>
+      <c r="I8">
+        <v>40</v>
+      </c>
+      <c r="J8">
+        <v>38</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="L8">
+        <f t="shared" ref="L8:L30" si="1">($K$36*G8*H8)/($K$35*TAN(RADIANS(K8)))*POWER(10,6)</f>
+        <v>21.48670431642153</v>
+      </c>
+      <c r="M8">
+        <f t="shared" ref="M8:M30" si="2">POWER(L8 - $K$33,2)</f>
+        <v>0.28897780587369115</v>
+      </c>
+    </row>
+    <row r="9" spans="6:13" x14ac:dyDescent="0.2">
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>40</v>
+      </c>
+      <c r="H9">
+        <v>136</v>
+      </c>
+      <c r="I9">
+        <v>49</v>
+      </c>
+      <c r="J9">
+        <v>52</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="0"/>
+        <v>50.5</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="1"/>
+        <v>21.674040750329656</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="2"/>
+        <v>0.12266114085973714</v>
+      </c>
+    </row>
+    <row r="10" spans="6:13" x14ac:dyDescent="0.2">
+      <c r="F10">
+        <v>4</v>
+      </c>
+      <c r="G10">
+        <v>40</v>
+      </c>
+      <c r="H10">
+        <v>212</v>
+      </c>
+      <c r="I10">
+        <v>59</v>
+      </c>
+      <c r="J10">
+        <v>66</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="0"/>
+        <v>62.5</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="1"/>
+        <v>21.335805526364663</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="2"/>
+        <v>0.47398453751615749</v>
+      </c>
+    </row>
+    <row r="11" spans="6:13" x14ac:dyDescent="0.2">
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="2">
+      <c r="H11">
+        <v>92</v>
+      </c>
+      <c r="I11">
+        <v>29</v>
+      </c>
+      <c r="J11">
+        <v>24</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="0"/>
+        <v>26.5</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="1"/>
+        <v>21.404216302594765</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="2"/>
+        <v>0.38446767388154918</v>
+      </c>
+    </row>
+    <row r="12" spans="6:13" x14ac:dyDescent="0.2">
+      <c r="F12">
+        <v>6</v>
+      </c>
+      <c r="G12">
+        <v>24</v>
+      </c>
+      <c r="H12">
+        <f>38*4</f>
+        <v>152</v>
+      </c>
+      <c r="I12">
+        <v>41</v>
+      </c>
+      <c r="J12">
+        <v>40</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="0"/>
+        <v>40.5</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="1"/>
+        <v>20.643933197332004</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="2"/>
+        <v>1.9053321068851981</v>
+      </c>
+    </row>
+    <row r="13" spans="6:13" x14ac:dyDescent="0.2">
+      <c r="F13">
+        <v>7</v>
+      </c>
+      <c r="G13">
+        <v>24</v>
+      </c>
+      <c r="H13">
+        <f>60*4</f>
+        <v>240</v>
+      </c>
+      <c r="I13">
+        <v>50</v>
+      </c>
+      <c r="J13">
+        <v>52</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="1"/>
+        <v>22.543856371315922</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="2"/>
+        <v>0.26996908704257644</v>
+      </c>
+    </row>
+    <row r="14" spans="6:13" x14ac:dyDescent="0.2">
+      <c r="F14">
+        <v>8</v>
+      </c>
+      <c r="G14">
+        <v>24</v>
+      </c>
+      <c r="H14">
+        <v>350</v>
+      </c>
+      <c r="I14">
+        <v>60</v>
+      </c>
+      <c r="J14">
+        <v>66</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="1"/>
+        <v>20.68624590026057</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="2"/>
+        <v>1.7903108354452828</v>
+      </c>
+    </row>
+    <row r="15" spans="6:13" x14ac:dyDescent="0.2">
+      <c r="F15">
+        <v>9</v>
+      </c>
+      <c r="G15">
+        <v>16</v>
+      </c>
+      <c r="H15">
+        <f>38*4</f>
+        <v>152</v>
+      </c>
+      <c r="I15">
+        <v>30</v>
+      </c>
+      <c r="J15">
+        <v>26</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="1"/>
+        <v>22.106791875334846</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="2"/>
+        <v>6.8097153470853666E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="6:13" x14ac:dyDescent="0.2">
+      <c r="F16">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>16</v>
+      </c>
+      <c r="H16">
+        <f>64*4</f>
+        <v>256</v>
+      </c>
+      <c r="I16">
+        <v>41</v>
+      </c>
+      <c r="J16">
+        <v>42</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="0"/>
+        <v>41.5</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="1"/>
+        <v>22.376287566535229</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="2"/>
+        <v>0.12391575048304647</v>
+      </c>
+    </row>
+    <row r="17" spans="6:13" x14ac:dyDescent="0.2">
+      <c r="F17">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>16</v>
+      </c>
+      <c r="H17">
+        <v>360</v>
+      </c>
+      <c r="I17">
+        <v>50</v>
+      </c>
+      <c r="J17">
+        <v>52</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="1"/>
+        <v>22.543856371315922</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="2"/>
+        <v>0.26996908704257644</v>
+      </c>
+    </row>
+    <row r="18" spans="6:13" x14ac:dyDescent="0.2">
+      <c r="F18">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="2"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
+      <c r="G18">
+        <v>16</v>
+      </c>
+      <c r="H18">
+        <v>560</v>
+      </c>
+      <c r="I18">
+        <v>60</v>
+      </c>
+      <c r="J18">
+        <v>64</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="1"/>
+        <v>23.026020648299802</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="2"/>
+        <v>1.0035026064952808</v>
+      </c>
+    </row>
+    <row r="19" spans="6:13" x14ac:dyDescent="0.2">
+      <c r="F19">
+        <v>13</v>
+      </c>
+      <c r="G19">
+        <v>12</v>
+      </c>
+      <c r="H19">
+        <f>52*4</f>
+        <v>208</v>
+      </c>
+      <c r="I19">
+        <v>30</v>
+      </c>
+      <c r="J19">
+        <v>26</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="1"/>
+        <v>22.688549556264711</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="2"/>
+        <v>0.44126616518192613</v>
+      </c>
+    </row>
+    <row r="20" spans="6:13" x14ac:dyDescent="0.2">
+      <c r="F20">
+        <v>14</v>
+      </c>
+      <c r="G20">
+        <v>12</v>
+      </c>
+      <c r="H20">
+        <v>340</v>
+      </c>
+      <c r="I20">
+        <v>40</v>
+      </c>
+      <c r="J20">
+        <v>42</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="1"/>
+        <v>22.684730558696995</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="2"/>
+        <v>0.4362069925951807</v>
+      </c>
+    </row>
+    <row r="21" spans="6:13" x14ac:dyDescent="0.2">
+      <c r="F21">
+        <v>15</v>
+      </c>
+      <c r="G21">
+        <v>12</v>
+      </c>
+      <c r="H21">
+        <v>490</v>
+      </c>
+      <c r="I21">
+        <v>50</v>
+      </c>
+      <c r="J21">
+        <v>52</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="1"/>
+        <v>23.013520045718337</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="2"/>
+        <v>0.97861391997859193</v>
+      </c>
+    </row>
+    <row r="22" spans="6:13" x14ac:dyDescent="0.2">
+      <c r="F22">
+        <v>16</v>
+      </c>
+      <c r="G22">
+        <v>12</v>
+      </c>
+      <c r="H22">
+        <f>38*20</f>
+        <v>760</v>
+      </c>
+      <c r="I22">
+        <v>60</v>
+      </c>
+      <c r="J22">
+        <v>66</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="1"/>
+        <v>22.459352691711477</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="2"/>
+        <v>0.18929618644643487</v>
+      </c>
+    </row>
+    <row r="33" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J33" t="s">
+        <v>11</v>
+      </c>
+      <c r="K33">
+        <f>AVERAGE(L7:L30)</f>
+        <v>22.024270875903881</v>
+      </c>
+    </row>
+    <row r="34" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="L34" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J35" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35">
+        <v>260</v>
+      </c>
+      <c r="L35">
+        <f>K35/1000</f>
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="36" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J36" t="s">
+        <v>7</v>
+      </c>
+      <c r="K36">
+        <f>4*PI()*POWER(10,-7)</f>
+        <v>1.2566370614359173E-6</v>
+      </c>
+    </row>
+    <row r="38" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J40" t="s">
+        <v>13</v>
+      </c>
+      <c r="K40">
+        <f>SQRT(SUM(M7:M30)/(COUNTA(M7:M30)*(COUNTA(M7:M30)-1)))</f>
+        <v>0.19128174822296531</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="A20:A25"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>